--- a/excel/baselines.xlsx
+++ b/excel/baselines.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\retail-demand-forecasting\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1CB6D9-F934-4225-9AC0-111A6C43C71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B18984-1355-479B-8902-BB156591F523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7810" yWindow="0" windowWidth="11480" windowHeight="12090" activeTab="1" xr2:uid="{F85AD8E0-2D22-4168-BD94-BF8429F15445}"/>
   </bookViews>
